--- a/public/file/Trax Book International Shipment Template.xlsx
+++ b/public/file/Trax Book International Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607DEC0A-2D14-4D61-92FC-9CA12319D81C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00B1089-C251-4BE5-A2A2-D7A5F05C8E5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Order Date (YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
   </si>
 </sst>
 </file>
@@ -443,33 +446,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -480,60 +484,63 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/public/file/Trax Book International Shipment Template.xlsx
+++ b/public/file/Trax Book International Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00B1089-C251-4BE5-A2A2-D7A5F05C8E5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE67C800-8BA2-420B-94C1-F588A83209AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Pieces</t>
-  </si>
-  <si>
-    <t>Self Collection</t>
   </si>
   <si>
     <t>Order Date (YYYY-MM-DD)</t>
@@ -446,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -457,23 +454,22 @@
     <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -484,7 +480,7 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -502,45 +498,42 @@
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/public/file/Trax Book International Shipment Template.xlsx
+++ b/public/file/Trax Book International Shipment Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE67C800-8BA2-420B-94C1-F588A83209AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84576482-6FA2-4898-9A2F-E1ECEFD7ED98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,12 +72,6 @@
     <t>Collection Amount</t>
   </si>
   <si>
-    <t>Consignee Phone Number 2 (03000000000)</t>
-  </si>
-  <si>
-    <t>Consignee Phone Number 1 (03000000000)</t>
-  </si>
-  <si>
     <t>Consignee City Name</t>
   </si>
   <si>
@@ -91,6 +85,12 @@
   </si>
   <si>
     <t>Postal Code</t>
+  </si>
+  <si>
+    <t>Consignee Phone Number 1</t>
+  </si>
+  <si>
+    <t>Consignee Phone Number 2</t>
   </si>
 </sst>
 </file>
@@ -477,10 +477,10 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -489,10 +489,10 @@
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -501,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>10</v>
@@ -531,10 +531,10 @@
         <v>9</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book International Shipment Template.xlsx
+++ b/public/file/Trax Book International Shipment Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84576482-6FA2-4898-9A2F-E1ECEFD7ED98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15F8D61-EE0E-4A3E-973C-8D625CE2226D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -91,6 +91,21 @@
   </si>
   <si>
     <t>Consignee Phone Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 1</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 2</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 3</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 4</t>
+  </si>
+  <si>
+    <t>Shipper Reference Number 5</t>
   </si>
 </sst>
 </file>
@@ -443,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -467,9 +482,10 @@
     <col min="20" max="20" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16.109375" style="1" customWidth="1"/>
+    <col min="23" max="27" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -535,6 +551,21 @@
       </c>
       <c r="V1" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
